--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00733-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00733-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCAC011A-068B-432C-81EE-A816AF759F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F0B08DC-5138-4392-A2EC-11BEC0E5E4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{0EBA6EEC-1C21-4581-A1FF-7BA80E517837}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{3D8E07FD-E8C9-4B9F-8A9A-E46920528454}"/>
   </bookViews>
   <sheets>
     <sheet name="00733-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1490,25 +1490,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F467DB7-31E1-4414-9857-D584BE0D320E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9DED8D4-2E84-48E1-90CA-58EB112C8014}">
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1536,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1566,7 +1566,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1662,7 +1662,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2020</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2019</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>25</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>25</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
         <v>49</v>
       </c>
